--- a/Outputs/metricas/oiec_pt/10_batches/comparativo_extracoes.xlsx
+++ b/Outputs/metricas/oiec_pt/10_batches/comparativo_extracoes.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Respostas ExtrativoPTOIE-DP" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Respostas ExtrativoDPTO-IE'!$A$1:$G$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Respostas ExtrativoDPTO-IE'!$A$1:$H$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Respostas ExtrativoOIEC-PT'!$A$1:$F$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Respostas ExtrativoPTOIE-DP'!$A$1:$G$101</definedName>
   </definedNames>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -464,6 +464,7 @@
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -489,15 +490,20 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>DptOIE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Gemini3.1Pro</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Grok4.0Fast</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>respostas_gpt5.5_mini</t>
         </is>
@@ -525,11 +531,9 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠ um casal → poderia abrir → quatro contas Teoricamente</t>
+              <sz val="10"/>
+            </rPr>
+            <t>um casal → poderia abrir → quatro contas Teoricamente</t>
           </r>
         </is>
       </c>
@@ -588,6 +592,32 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ um casal → poderia abrir → quatro contas Teoricamente</t>
+          </r>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ um casal → poderia abrir → quatro contas Tesco</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -595,7 +625,7 @@
           </r>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -620,7 +650,7 @@
           </r>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -709,6 +739,90 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ os clientes de o Banco de a Escócia → ganham → 3 %</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os clientes de o Banco de a Escócia → ganham → 3 % em balanços de £</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os clientes de o Banco de a Escócia → ganham → 3 % em balanços de £ 3,000 - £ 5,000</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os clientes de o Banco de a Escócia → ganham → 3 % em balanços de £ 3,000 - £ 5,000 quando adicionam a opção gratuita Vantage a as suas contas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os clientes de o Banco de a Escócia → ganham → 3 % Entretanto</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os clientes de o Banco de a Escócia → ganham → 3 % 3,000 - £ 5,000</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os clientes de o Banco de a Escócia → ganham → 3 % quando adicionam a opção gratuita Vantage a as suas contas</t>
+          </r>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ os clientes do Banco da Escócia → ganham → 3% em balanços de £3,000-£5,000</t>
           </r>
           <r>
@@ -725,7 +839,7 @@
           </r>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -749,7 +863,7 @@
           </r>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -837,6 +951,18 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ você → é → capaz de acessar seu dinheiro</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ você → é → capaz de acessar seu dinheiro sempre que quiser</t>
           </r>
           <r>
@@ -849,6 +975,42 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ você → é → capaz de acessar seu dinheiro sempre Com isto</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ você → é → capaz de acessar seu dinheiro sempre Com isto , em teoria</t>
+          </r>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ você → é → capaz de acessar seu dinheiro sempre que quiser</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ você → é capaz de acessar → seu dinheiro sempre que quiser</t>
           </r>
           <r>
@@ -865,7 +1027,7 @@
           </r>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -889,7 +1051,7 @@
           </r>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -977,6 +1139,54 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Esta taxa de 3 % → também se aplica → titulares de cartão Nectar</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Esta taxa de 3 % → também se aplica → titulares de cartão Nectar que pensam em pedir emprestado 15,001 - £ 19,999</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Esta taxa de 3 % → também se aplica → titulares de cartão Nectar que pensam em pedir emprestado 15,001 - £ 19,999 , durante um período de dois a três anos</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Esta taxa de 3 % → também se aplica → titulares de cartão Nectar que pensam , durante um período de dois a três anos</t>
+          </r>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ Esta taxa de 3% → também se aplica a → titulares de cartão Nectar</t>
           </r>
           <r>
@@ -1017,7 +1227,7 @@
           </r>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1041,7 +1251,7 @@
           </r>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1088,11 +1298,9 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠ O enxofre → é → um nutriente vital</t>
+              <sz val="10"/>
+            </rPr>
+            <t>O enxofre → é → um nutriente vital</t>
           </r>
           <r>
             <t>
@@ -1114,11 +1322,9 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠ O enxofre → é um nutriente vital para → o crescimento saudável de as plantas</t>
+              <sz val="10"/>
+            </rPr>
+            <t>O enxofre → é um nutriente vital para → o crescimento saudável de as plantas</t>
           </r>
           <r>
             <t>
@@ -1176,6 +1382,91 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓ O enxofre → é um nutriente → vital para o crescimento saudável de as plantas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O enxofre → é um nutriente → vital para o crescimento saudável de as plantas , mas os solos en o Reino Unido são naturalmente deficientes deste mineral</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O enxofre → é um nutriente → para o crescimento saudável de as plantas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O enxofre → é um nutriente → mas os solos en o Reino Unido são naturalmente deficientes deste mineral</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓ os solos en o Reino Unido → são → naturalmente deficientes deste mineral</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ O enxofre → é → um nutriente vital</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O enxofre → é → os solos en o Reino Unido são naturalmente deficientes deste mineral</t>
+          </r>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -1195,7 +1486,7 @@
           </r>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1219,7 +1510,7 @@
           </r>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1292,6 +1583,54 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Um avanço → rápido → para 2016</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Um avanço → rápido → para 2016 e isso é cada vez mais digno de atenção</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Um avanço → rápido → e isso é cada vez mais digno de atenção</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ isso → é cada vez → mais digno de atenção</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
               <color rgb="001E7A34"/>
               <sz val="10"/>
@@ -1314,6 +1653,19 @@
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ isso → é → cada vez mais digno de atenção</t>
+          </r>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1374,6 +1726,18 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ como Surpreendentemente parecer , até as nuvens de chuvas ácidas → podem ter → um lado positivo</t>
+          </r>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
@@ -1381,7 +1745,7 @@
           </r>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1393,7 +1757,7 @@
           </r>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1429,11 +1793,9 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠ alguém → tem → dignidade</t>
+              <sz val="10"/>
+            </rPr>
+            <t>alguém → tem → dignidade</t>
           </r>
           <r>
             <t>
@@ -1453,11 +1815,9 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠ alguém → tem → dignidade por o menos</t>
+              <sz val="10"/>
+            </rPr>
+            <t>alguém → tem → dignidade por o menos</t>
           </r>
           <r>
             <t>
@@ -1539,10 +1899,61 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O mundo → pode estar → enfurecido - e absurdo en o entanto</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
               <color rgb="001E7A34"/>
               <sz val="10"/>
             </rPr>
+            <t>✓✓ alguém → tem → dignidade</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ alguém → tem → dignidade para continuar a protestar contra esse fato</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ alguém → tem → dignidade por o menos</t>
+          </r>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓✓ O mundo → pode estar → enfurecido</t>
           </r>
           <r>
@@ -1572,7 +1983,7 @@
           </r>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1611,7 +2022,7 @@
           </r>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1715,11 +2126,23 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Acaba → ouvindo → mais intensamente o barulho seguinte</t>
+          </r>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t xml:space="preserve">✗ ele → surge → </t>
           </r>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1743,7 +2166,7 @@
           </r>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1875,6 +2298,19 @@
           </r>
         </is>
       </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ Isso → é → legitimamente horrível</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1947,6 +2383,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -1979,7 +2428,7 @@
           </r>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2016,7 +2465,7 @@
           </r>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2149,6 +2598,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -2168,7 +2630,7 @@
           </r>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2192,7 +2654,7 @@
           </r>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2365,6 +2827,90 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Catalano → voltou → para a área</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Catalano → voltou → para a área depois de viver em Londres</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Catalano → voltou → para a área depois de viver em Londres e em Glasgow , onde estudou design de jóias</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Catalano → voltou → para a área depois de viver em Londres e em Glasgow , onde estudou design de jóias en a Glasgow School of Art</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Catalano → voltou → depois de viver em Londres</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Catalano → voltou → depois de viver e em Glasgow , onde estudou design de jóias</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Catalano → voltou → depois de viver e em Glasgow , onde estudou en a Glasgow School of Art</t>
+          </r>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ Catalano → voltou → para a área depois de viver em Londres e em Glasgow</t>
           </r>
           <r>
@@ -2393,7 +2939,7 @@
           </r>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2441,7 +2987,7 @@
           </r>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2564,6 +3110,31 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="00B8860B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>🟡 Eu → adorei → as cores tropicais</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Eu → adorei → as cores tropicais , diz ele</t>
+          </r>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -2584,7 +3155,7 @@
           </r>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2609,7 +3180,7 @@
           </r>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2646,11 +3217,9 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠ Eu → visitei → os espetáculos universitários</t>
+              <sz val="10"/>
+            </rPr>
+            <t>Eu → visitei → os espetáculos universitários</t>
           </r>
           <r>
             <t>
@@ -2670,11 +3239,9 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠ Eu → visitei → os espetáculos universitários em a Universidade de Northampton para encontrar novos talentos</t>
+              <sz val="10"/>
+            </rPr>
+            <t>Eu → visitei → os espetáculos universitários em a Universidade de Northampton para encontrar novos talentos</t>
           </r>
           <r>
             <t>
@@ -2757,6 +3324,79 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ Eu → visitei → os espetáculos universitários</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓ Eu → visitei → os espetáculos universitários en a Universidade de Northampton</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓ Eu → visitei → os espetáculos universitários en a Universidade de Northampton para encontrar novos talentos</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Eu → visitei → os espetáculos universitários en a Universidade de Northampton para encontrar novos talentos , diz</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Eu → visitei → os espetáculos universitários para encontrar novos talentos</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Eu → visitei → os espetáculos universitários , diz</t>
+          </r>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -2788,7 +3428,7 @@
           </r>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2812,7 +3452,7 @@
           </r>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2950,6 +3590,43 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t xml:space="preserve">✗ eu → sugiro → </t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ ela → use → a Frank</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="00B8860B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>🟡 ela → use → a Frank como sua modelo</t>
+          </r>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ ela → ri → quando eu sugiro que ela use a Frank como sua modelo</t>
           </r>
           <r>
@@ -2979,7 +3656,7 @@
           </r>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3016,7 +3693,7 @@
           </r>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3065,11 +3742,9 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠ a paisagem de o escritório → apresenta → muitas roupas</t>
+              <sz val="10"/>
+            </rPr>
+            <t>a paisagem de o escritório → apresenta → muitas roupas</t>
           </r>
           <r>
             <t>
@@ -3130,6 +3805,43 @@
               <color rgb="001E7A34"/>
               <sz val="10"/>
             </rPr>
+            <t>✓✓ a paisagem de o escritório → apresenta → muitas roupas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a paisagem de o escritório → apresenta → muitas roupas e , en o sentido de comida , pouco</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓ a paisagem de o escritório → apresenta → muitas roupas Naturalmente</t>
+          </r>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓✓ a paisagem do escritório → apresenta → muitas roupas</t>
           </r>
           <r>
@@ -3146,7 +3858,7 @@
           </r>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3171,7 +3883,7 @@
           </r>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3221,11 +3933,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 A própria Wintour → aparece → rapidamente</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A própria Wintour → aparece → rapidamente</t>
           </r>
           <r>
             <t>
@@ -3270,11 +3981,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 A própria Wintour → aparece → rapidamente</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A própria Wintour → aparece → rapidamente</t>
           </r>
         </is>
       </c>
@@ -3283,11 +3993,23 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 A própria Wintour → aparece → rapidamente</t>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A própria Wintour → aparece → rapidamente</t>
           </r>
           <r>
             <t>
@@ -3303,16 +4025,15 @@
           </r>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 A própria Wintour → aparece → rapidamente</t>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A própria Wintour → aparece → rapidamente</t>
           </r>
           <r>
             <t>
@@ -3328,16 +4049,15 @@
           </r>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 A própria Wintour → aparece → rapidamente</t>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A própria Wintour → aparece → rapidamente</t>
           </r>
           <r>
             <t>
@@ -3453,6 +4173,18 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ que → pareciam ser → de os anos 70</t>
+          </r>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ a cara desta mulher → continuava a surgir → em fotografias que pareciam ser dos anos 70</t>
           </r>
           <r>
@@ -3469,7 +4201,7 @@
           </r>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3505,7 +4237,7 @@
           </r>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3629,11 +4361,23 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Amo → jogar → com isso</t>
+          </r>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t xml:space="preserve">✗ musas → se encaixem → </t>
           </r>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3669,7 +4413,7 @@
           </r>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3804,6 +4548,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -3823,7 +4580,7 @@
           </r>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3990,6 +4747,30 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ uma proibição ou um licenciamento → fosse → com base nestes fundamentos</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ uma proibição ou um licenciamento → fosse → com base nestes fundamentos ""</t>
+          </r>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
@@ -4081,7 +4862,7 @@
           </r>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4141,7 +4922,7 @@
           </r>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4166,11 +4947,9 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠ A postura de o RSPB → também o colocou em → conflito com muitos líderes conservadores desde o autor de a petição</t>
+              <sz val="10"/>
+            </rPr>
+            <t>A postura de o RSPB → também o colocou em → conflito com muitos líderes conservadores desde o autor de a petição</t>
           </r>
           <r>
             <t>
@@ -4310,9 +5089,81 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A postura de o RSPB → também o colocou → em conflito</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
+            <t>✓ A postura de o RSPB → também o colocou → em conflito com muitos líderes conservadores , desde o autor de a petição</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓ A postura de o RSPB → também o colocou → em conflito com muitos líderes conservadores , desde o autor de a petição , Mark Avery , a o apresentador de TV Chris Packham</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A postura de o RSPB → também o colocou → com muitos líderes conservadores , desde o autor de a petição</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A postura de o RSPB → também o colocou → com muitos líderes conservadores , desde o autor</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A postura de o RSPB → também o colocou → com muitos líderes conservadores , desde o autor Mark Avery , a o apresentador de TV Chris Packham</t>
+          </r>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓ A postura do RSPB → também o colocou → em conflito com muitos líderes conservadores, desde o autor da petição, Mark Avery, ao apresentador de TV Chris Packham</t>
           </r>
           <r>
@@ -4377,7 +5228,7 @@
           </r>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4437,7 +5288,7 @@
           </r>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4549,6 +5400,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="00B8860B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>🟡 ele → está → errado</t>
+          </r>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -4569,7 +5433,7 @@
           </r>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4679,6 +5543,19 @@
           </r>
         </is>
       </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -4792,6 +5669,42 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Nisto → será → em pleno sábado</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ países desenvolvidos → se questionam → publicamente sobre seus planos e ambições</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ países desenvolvidos → se questionam → sobre seus planos e ambições</t>
+          </r>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ um ponto diário em Marrocos → será → em pleno sábado, quando países desenvolvidos se questionam publicamente sobre seus planos e ambições</t>
           </r>
           <r>
@@ -4844,7 +5757,7 @@
           </r>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4868,7 +5781,7 @@
           </r>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4957,11 +5870,35 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ que → tenham → uma posição real</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ que → tenham → uma posição real en o projeto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ aqueles → tenham → uma posição real no projeto</t>
           </r>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4973,7 +5910,7 @@
           </r>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5085,6 +6022,42 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ O bacalhau de o mar → pode colapsar → sem os limites propostos</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O bacalhau de o mar → pode colapsar → sem os limites propostos , disse um oficial de a UE</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O bacalhau de o mar → pode colapsar → disse um oficial de a UE</t>
+          </r>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ um oficial da UE → disse → O bacalhau do mar Céltico pode colapsar, sem os limites propostos</t>
           </r>
           <r>
@@ -5101,7 +6074,7 @@
           </r>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5125,7 +6098,7 @@
           </r>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5261,6 +6234,42 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ grandes promoções para o bacalhau , a solha → foram também previstas → o linguado</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ grandes promoções para o bacalhau , a solha → foram também previstas → o linguado , o linguado - areeiro e o escamudo , en os mares Celtas e Irlandeses</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ grandes promoções para o bacalhau , a solha → foram também previstas → o linguado o linguado - areeiro e o escamudo , en os mares Celtas e Irlandeses</t>
+          </r>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ grandes promoções para o bacalhau, a solha, o linguado, o linguado-areeiro e o escamudo → foram também previstas → nos mares Celtas e Irlandeses</t>
           </r>
           <r>
@@ -5325,7 +6334,7 @@
           </r>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5337,7 +6346,7 @@
           </r>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5445,6 +6454,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ Os conservacionistas → saudaram → o anúncio de a comissão</t>
+          </r>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
@@ -5452,7 +6474,7 @@
           </r>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5464,7 +6486,7 @@
           </r>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5525,6 +6547,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
               <color rgb="001E7A34"/>
               <sz val="10"/>
@@ -5533,7 +6568,7 @@
           </r>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5546,7 +6581,7 @@
           </r>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5683,6 +6718,66 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ O → Agora foi → apenas por convite</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O → Agora foi → por convite</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Agora foi apenas por convite → acrescenta → o Dr. Lee</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ muitos destes mercados → estão → facilmente acessíveis</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ você → souber → pesquisar como</t>
+          </r>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ o Dr. Lee → acrescenta → O Agora foi apenas por convite, mas muitos destes mercados estão facilmente acessíveis se você souber como pesquisar</t>
           </r>
           <r>
@@ -5723,7 +6818,7 @@
           </r>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5759,7 +6854,7 @@
           </r>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5893,6 +6988,42 @@
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
+            <t>✓ Eles → não os tinham → en o nosso tempo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Eles → não os tinham → en o nosso tempo , e pessoas sem crianças se expressam através de a sua desaprovação , o seu ódio por a parentalidade moderna</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Eles → não os tinham → o seu ódio por a parentalidade moderna</t>
+          </r>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓ Eles → não os tinham → no nosso tempo</t>
           </r>
           <r>
@@ -5909,7 +7040,7 @@
           </r>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5933,7 +7064,7 @@
           </r>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6032,6 +7163,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -6039,7 +7183,7 @@
           </r>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6126,6 +7270,54 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ eu → estava → de volta</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓ eu → estava → de volta en o EMicro</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ eu → estava → Dia três</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ eu → estava → en o EMicro</t>
+          </r>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ eu → estava de volta → no EMicro Dia três</t>
           </r>
           <r>
@@ -6142,7 +7334,7 @@
           </r>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6154,7 +7346,7 @@
           </r>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6191,11 +7383,9 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠ o Reino Unido → está enfrentando → uma escassez de pessoas</t>
+              <sz val="10"/>
+            </rPr>
+            <t>o Reino Unido → está enfrentando → uma escassez de pessoas</t>
           </r>
         </is>
       </c>
@@ -6240,6 +7430,31 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ o Reino Unido → está enfrentando → uma escassez de pessoas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ o Reino Unido → está enfrentando → uma escassez de pessoas , por extensão</t>
+          </r>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -6259,7 +7474,7 @@
           </r>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6283,7 +7498,7 @@
           </r>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6332,11 +7547,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 As empresas → podem tentar criar → um firewall entre sistemas sensíveis e potências estrangeiras</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ As empresas → podem tentar criar → um firewall entre sistemas sensíveis e potências estrangeiras</t>
           </r>
           <r>
             <t>
@@ -6357,11 +7571,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 As empresas → podem tentar criar → um firewall entre sistemas sensíveis e potências estrangeiras</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ As empresas → podem tentar criar → um firewall entre sistemas sensíveis e potências estrangeiras</t>
           </r>
         </is>
       </c>
@@ -6370,11 +7583,22 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 As empresas → podem tentar criar → um firewall entre sistemas sensíveis e potências estrangeiras</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ As empresas → podem tentar → criar um firewall entre sistemas sensíveis e potências estrangeiras</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ As empresas → podem tentar → criar um firewall entre sistemas sensíveis e potências estrangeiras , mas nem sempre funciona</t>
           </r>
         </is>
       </c>
@@ -6383,11 +7607,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 As empresas → podem tentar criar → um firewall entre sistemas sensíveis e potências estrangeiras</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ As empresas → podem tentar criar → um firewall entre sistemas sensíveis e potências estrangeiras</t>
           </r>
         </is>
       </c>
@@ -6396,11 +7619,22 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 As empresas → podem tentar criar → um firewall entre sistemas sensíveis e potências estrangeiras</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ As empresas → podem tentar criar → um firewall entre sistemas sensíveis e potências estrangeiras</t>
+          </r>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ As empresas → podem tentar criar → um firewall entre sistemas sensíveis e potências estrangeiras</t>
           </r>
           <r>
             <t>
@@ -6441,11 +7675,9 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠ eles → podem por o menos colocar → armadilhas</t>
+              <sz val="10"/>
+            </rPr>
+            <t>eles → podem por o menos colocar → armadilhas</t>
           </r>
           <r>
             <t>
@@ -6526,6 +7758,31 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ eles → podem por o menos colocar → armadilhas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ eles → podem por o menos colocar → armadilhas para confundir e impedir - um conceito conhecido como "" defesa ativa ""</t>
+          </r>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -6533,7 +7790,7 @@
           </r>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6557,7 +7814,7 @@
           </r>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6605,11 +7862,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 a minha lista → cresceu → muito</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a minha lista → cresceu → muito</t>
           </r>
           <r>
             <t>
@@ -6630,11 +7886,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 a minha lista → cresceu → muito</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a minha lista → cresceu → muito</t>
           </r>
         </is>
       </c>
@@ -6646,6 +7901,30 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ a minha lista → cresceu → Depois de ter descoberto uma rica discussão en a internet</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a minha lista → cresceu → Depois de ter descoberto uma rica discussão en a internet sobre o assunto</t>
+          </r>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ a minha lista → cresceu → muito Depois de ter descoberto uma rica discussão na internet sobre o assunto</t>
           </r>
           <r>
@@ -6655,11 +7934,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 a minha lista → cresceu → muito</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a minha lista → cresceu → muito</t>
           </r>
           <r>
             <t>
@@ -6687,16 +7965,15 @@
           </r>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 a minha lista → cresceu → muito</t>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a minha lista → cresceu → muito</t>
           </r>
           <r>
             <t>
@@ -6712,7 +7989,7 @@
           </r>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6729,11 +8006,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 a minha lista → cresceu → muito</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a minha lista → cresceu → muito</t>
           </r>
           <r>
             <t>
@@ -6832,6 +8108,19 @@
           </r>
         </is>
       </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ Eu → avistei → algumas</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -6906,6 +8195,18 @@
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
+            <t>✓ A minha próxima parada → foi → Bellingham , bem perto de a fronteira canadense</t>
+          </r>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓ A minha próxima parada → foi → Bellingham, bem perto da fronteira canadense</t>
           </r>
           <r>
@@ -6923,7 +8224,7 @@
           </r>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6935,7 +8236,7 @@
           </r>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7011,6 +8312,18 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ volta nós a o trem → continuamos → em direção a o o sul</t>
+          </r>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ nós → continuamos → em direção ao o sul De volta ao trem</t>
           </r>
           <r>
@@ -7027,7 +8340,7 @@
           </r>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7039,7 +8352,7 @@
           </r>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7112,6 +8425,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -7131,7 +8457,7 @@
           </r>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7143,7 +8469,7 @@
           </r>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7330,6 +8656,67 @@
               <color rgb="001E7A34"/>
               <sz val="10"/>
             </rPr>
+            <t>✓✓ um guarda de chapéu vermelho → comanda → a plataforma</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um guarda de chapéu vermelho → comanda → a plataforma e um trabalhador anda a o longo de o trem</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um guarda de chapéu vermelho → comanda → a plataforma e um trabalhador anda a o longo de o trem com um martelo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um guarda de chapéu vermelho → comanda → a plataforma e um trabalhador anda a o longo de o trem com um martelo , batendo gentilmente</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um guarda de chapéu vermelho → comanda → a plataforma e um trabalhador anda a o longo de o trem com um martelo , batendo gentilmente en a parte de baixo de a carruagem</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓✓ um guarda de chapéu vermelho → comanda → a plataforma Em cada estação</t>
           </r>
           <r>
@@ -7339,10 +8726,143 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um guarda de chapéu vermelho → comanda → a plataforma com um martelo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um guarda de chapéu vermelho → comanda → a plataforma , batendo gentilmente</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um guarda de chapéu vermelho → comanda → a plataforma , batendo en a parte de baixo de a carruagem</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um trabalhador → anda → a o longo de o trem</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um trabalhador → anda → a o longo de o trem com um martelo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um trabalhador → anda → a o longo de o trem com um martelo , batendo gentilmente</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um trabalhador → anda → a o longo de o trem com um martelo , batendo gentilmente en a parte de baixo de a carruagem</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um trabalhador → anda → com um martelo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um trabalhador → anda → batendo gentilmente</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ um trabalhador → anda → batendo en a parte de baixo de a carruagem</t>
+          </r>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
               <color rgb="001E7A34"/>
               <sz val="10"/>
             </rPr>
+            <t>✓✓ um guarda de chapéu vermelho → comanda → a plataforma Em cada estação</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓✓ um guarda de chapéu vermelho → comanda → a plataforma</t>
           </r>
           <r>
@@ -7383,7 +8903,7 @@
           </r>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7408,7 +8928,7 @@
           </r>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7506,6 +9026,30 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">✗ pirulitos de arroz → são consideradas um petisco → </t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ pirulitos de arroz → são consideradas → um petisco</t>
+          </r>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
               <color rgb="001E7A34"/>
               <sz val="10"/>
@@ -7514,7 +9058,7 @@
           </r>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7527,7 +9071,7 @@
           </r>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7707,6 +9251,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -7727,7 +9284,7 @@
           </r>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7739,7 +9296,7 @@
           </r>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7847,9 +9404,34 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ O juramento → envolve → legisladores jurando lealdade a Hong Kong</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
+            <t>✓ O juramento → envolve → legisladores jurando lealdade a Hong Kong , como parte de a República Popular de a China</t>
+          </r>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓ O juramento → envolve → legisladores jurando lealdade a Hong Kong, como parte da República Popular da China</t>
           </r>
           <r>
@@ -7878,7 +9460,7 @@
           </r>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7890,7 +9472,7 @@
           </r>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8015,6 +9597,31 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ que → é liderado → por legisladores pró - Pequim</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="00B8860B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>🟡 o par → não deve tomar → posse</t>
+          </r>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ O governo de Hong Kong → argumentou → que o par não deve tomar posse</t>
           </r>
           <r>
@@ -8045,7 +9652,7 @@
           </r>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8082,7 +9689,7 @@
           </r>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8219,6 +9826,54 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ a sua intervenção → é → necessária</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a sua intervenção → é → necessária para evitar a paralisia legislativa contínua</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a sua intervenção → é → necessária para evitar a paralisia legislativa contínua en a cidade</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a sua intervenção → é → necessária en a cidade</t>
+          </r>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ ele → disse → Pequim acredita que a sua intervenção é necessária para evitar a paralisia legislativa contínua na cidade</t>
           </r>
           <r>
@@ -8259,7 +9914,7 @@
           </r>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8295,7 +9950,7 @@
           </r>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8382,11 +10037,47 @@
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
+            <t>✓ Hong Kong → estar se preparando → para uma onda de protestos</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Hong Kong → estar se preparando → Entretanto</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Hong Kong → estar se preparando → Entretanto , parece</t>
+          </r>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓ Hong Kong → parece estar se preparando → para uma onda de protestos</t>
           </r>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8398,7 +10089,7 @@
           </r>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8510,6 +10201,30 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Ele → disse → en o Andrew Marr Show de a BBC</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ o Governo → quer → que</t>
+          </r>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ Ele → disse → no Andrew Marr Show da BBC: "Uma eleição legislativa é francamente a última coisa que o Governo quer."</t>
           </r>
           <r>
@@ -8562,7 +10277,7 @@
           </r>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8598,7 +10313,7 @@
           </r>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8661,6 +10376,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -8668,7 +10396,7 @@
           </r>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8680,7 +10408,7 @@
           </r>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8768,6 +10496,30 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ um jogo → é → simples de esquecer</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ você → dominou → que</t>
+          </r>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ Empatar um jogo que você dominou → é → simples de esquecer</t>
           </r>
           <r>
@@ -8796,7 +10548,7 @@
           </r>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8832,7 +10584,7 @@
           </r>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8942,6 +10694,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -8961,7 +10726,7 @@
           </r>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8985,7 +10750,7 @@
           </r>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9095,6 +10860,30 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Esse → foi → sem dúvida</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ o caso de Andy → foi → sem dúvida</t>
+          </r>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ Esse → foi → sem dúvida, o caso de Andy quando enfrentou Benoît Paire, em Monte Carlo, em abril</t>
           </r>
           <r>
@@ -9124,7 +10913,7 @@
           </r>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9148,7 +10937,7 @@
           </r>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9242,6 +11031,103 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ tudo → está → fora de questão</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ tudo → está → fora de questão e ele parece estar a a procura de respostas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ tudo → está → fora de questão e ele parece estar a a procura de respostas a toda hora</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ tudo → está → agora</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ tudo → está → e ele parece estar a a procura de respostas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ tudo → está → e ele parece estar a toda hora</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ ele → parece → estar a a procura de respostas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ ele → parece → estar a a procura de respostas a toda hora</t>
+          </r>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -9286,7 +11172,7 @@
           </r>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9311,7 +11197,7 @@
           </r>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9411,6 +11297,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="00B8860B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>🟡 a Taça Davis → desempenhou → algum papel</t>
+          </r>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -9431,7 +11330,7 @@
           </r>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9456,7 +11355,7 @@
           </r>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9557,6 +11456,18 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ A pesquisa anual → também revelou → que as preocupações sobre assumir novos encargos financeiros</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ A pesquisa anual → também revelou → que as preocupações sobre assumir novos encargos financeiros têm disparado</t>
           </r>
           <r>
@@ -9569,11 +11480,35 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ A pesquisa anual → também revelou → que as preocupações sobre assumir têm disparado</t>
+          </r>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A pesquisa anual → também revelou → que as preocupações sobre assumir novos encargos financeiros têm disparado</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t xml:space="preserve">✗ as preocupações sobre assumir novos encargos financeiros → têm disparado → </t>
           </r>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9597,7 +11532,7 @@
           </r>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9719,6 +11654,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -9739,7 +11687,7 @@
           </r>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9764,7 +11712,7 @@
           </r>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9922,6 +11870,67 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ A notícia de a fraude de a companhia - → limpou → dezenas de bilhões de euros de o valor de a VW</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A notícia de a fraude de a companhia - → limpou → dezenas de bilhões de euros de o valor de a VW , Martin Winterkorn</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A notícia de a fraude de a companhia - → limpou → dezenas de bilhões de euros de o valor de a VW , Martin Winterkorn , o seu trabalho</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A notícia de a fraude de a companhia - → limpou → dezenas de bilhões de euros de o valor de a VW durante anos -</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A notícia de a fraude de a companhia - → limpou → dezenas de bilhões de euros de o valor de a VW o seu trabalho</t>
+          </r>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
@@ -9989,7 +11998,7 @@
           </r>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10049,7 +12058,7 @@
           </r>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10254,6 +12263,18 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Isso → também abriu → a VW</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
               <color rgb="001E7A34"/>
               <sz val="10"/>
@@ -10267,10 +12288,71 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ elas → levarem → mais que € 16 bilhões</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ elas → levarem → mais que € 16 bilhões de provisões</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ elas → levarem → que € 16 bilhões</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ elas → levarem → que € de provisões</t>
+          </r>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
               <color rgb="001E7A34"/>
               <sz val="10"/>
             </rPr>
+            <t>✓✓ Isso → também abriu → a VW para reivindicações e ações legais imensas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓✓ Isso → também abriu → a VW para reivindicações</t>
           </r>
           <r>
@@ -10312,7 +12394,7 @@
           </r>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10349,7 +12431,7 @@
           </r>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10546,6 +12628,102 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ A sondagem → começou → em junho</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A sondagem → começou → em junho , com foco en o Sr. Winterkorn</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A sondagem → começou → em junho , com foco en o Sr. Winterkorn e en o chefe de marca , Herbert Diess</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A sondagem → começou → em junho , com foco en o Sr. Winterkorn e en o chefe de marca , Herbert Diess , que permanece en a fabricante de automóveis</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A sondagem → começou → com foco en o Sr. Winterkorn</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A sondagem → começou → com foco en o Sr. e en o chefe de marca , Herbert Diess</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A sondagem → começou → com foco en o Sr. , que permanece en a fabricante de automóveis</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ que → permanece → en a fabricante de automóveis</t>
+          </r>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ A sondagem → começou → em junho, com foco no Sr. Winterkorn e no chefe de marca, Herbert Diess, que permanece na fabricante de automóveis.</t>
           </r>
           <r>
@@ -10634,7 +12812,7 @@
           </r>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10682,7 +12860,7 @@
           </r>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="H63" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10873,6 +13051,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -10905,7 +13096,7 @@
           </r>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10929,7 +13120,7 @@
           </r>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11026,6 +13217,42 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ As empresas → esperavam → começar a decrescer em julho</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ As empresas → esperavam → começar a decrescer em julho , imediatamente após o voto de o Brexit</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ As empresas → esperavam → começar a decrescer em julho , imediatamente após o voto de o Brexit , mas em vez disso têm conseguido manter o crescimento constante</t>
+          </r>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
@@ -11069,7 +13296,7 @@
           </r>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11093,7 +13320,7 @@
           </r>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11229,6 +13456,30 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Os negócios de varejo → também cresceram → se expandiram , uma vez que os lojistas continuam otimistas e as companhias de serviço a o cliente</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓ que os lojistas → continuam → otimistas</t>
+          </r>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ Os negócios de varejo e atacado → se expandiram → uma vez que os lojistas continuam otimistas e as companhias de serviço ao cliente também cresceram</t>
           </r>
           <r>
@@ -11282,7 +13533,7 @@
           </r>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11319,7 +13570,7 @@
           </r>
         </is>
       </c>
-      <c r="G66" s="3" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11454,6 +13705,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ o Governo → ainda tem → um grande déficit orçamental</t>
+          </r>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -11486,7 +13750,7 @@
           </r>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11511,7 +13775,7 @@
           </r>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="H67" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11561,11 +13825,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 O custo → vai mudar → mensalmente</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O custo → vai mudar → mensalmente</t>
           </r>
           <r>
             <t>
@@ -11598,11 +13861,10 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 O custo → vai mudar → mensalmente</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O custo → vai mudar → mensalmente</t>
           </r>
           <r>
             <t>
@@ -11635,11 +13897,34 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 O custo → vai mudar → mensalmente</t>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ o preço → aumente → en o inverno</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ preço que aumente , tal → aumenta → como o uso</t>
+          </r>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O custo → vai mudar → mensalmente</t>
           </r>
           <r>
             <t>
@@ -11691,16 +13976,15 @@
           </r>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 O custo → vai mudar → mensalmente</t>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O custo → vai mudar → mensalmente</t>
           </r>
           <r>
             <t>
@@ -11728,16 +14012,15 @@
           </r>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00B8860B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>🟡 O custo → vai mudar → mensalmente</t>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O custo → vai mudar → mensalmente</t>
           </r>
           <r>
             <t>
@@ -11899,6 +14182,54 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A taxa fixa de a Eon → custa → 760 e os clientes de a Avro Energy</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A taxa fixa de a Eon → custa → 760 e os clientes de a Avro Energy pagariam £ 760</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A taxa fixa de a Eon → custa → 760 e os clientes de a Avro Energy pagariam £ 760 por a sua tarifa Simple and</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A taxa fixa de a Eon → custa → 760 e os clientes de a Avro Energy por a sua tarifa Simple and</t>
+          </r>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <b val="1"/>
               <color rgb="001E7A34"/>
               <sz val="10"/>
@@ -11931,7 +14262,7 @@
           </r>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11956,7 +14287,7 @@
           </r>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12043,30 +14374,6 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>✗  → é → um classe cara</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>✗  → é → uma tarifa de pré-pagamento</t>
-          </r>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
               <i val="1"/>
               <color rgb="00888888"/>
               <sz val="10"/>
@@ -12075,7 +14382,44 @@
           </r>
         </is>
       </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗  → é → um classe cara</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗  → é → uma tarifa de pré-pagamento</t>
+          </r>
+        </is>
+      </c>
       <c r="G70" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12152,6 +14496,30 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Um investidor com alguma sorte e £ 10,000 em títulos → poderia esperar → receber £ 125 em prêmios</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Um investidor com alguma sorte e £ 10,000 em títulos → poderia esperar → receber £ 125 em prêmios , por ano</t>
+          </r>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ Um investidor com alguma sorte e £10,000 em títulos → poderia esperar receber → £125 em prêmios, por ano</t>
           </r>
           <r>
@@ -12192,7 +14560,7 @@
           </r>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12204,7 +14572,7 @@
           </r>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12292,6 +14660,30 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t xml:space="preserve">✗ eles → o fizessem → </t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a Premium Bonds → seria → indistinguível de as contas poupança comuns</t>
+          </r>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ a Premium Bonds → seria → indistinguível das contas poupança comuns Se eles o fizessem</t>
           </r>
           <r>
@@ -12320,7 +14712,7 @@
           </r>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12332,7 +14724,7 @@
           </r>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12417,6 +14809,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -12448,7 +14853,7 @@
           </r>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12460,7 +14865,7 @@
           </r>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12548,6 +14953,30 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Isso → não impediu → os investidores de se reunirem para colocar o seu dinheiro</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Isso → não impediu → os investidores de se reunirem para colocar o seu dinheiro en os fundos</t>
+          </r>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ Isso → não impediu → os investidores de se reunirem para colocar o seu dinheiro nos fundos</t>
           </r>
           <r>
@@ -12564,7 +14993,7 @@
           </r>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12576,7 +15005,7 @@
           </r>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12699,6 +15128,42 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Ele → foi seguido → por os fundos Aviva Investors Multi Strategy Target Return and</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓ os investidores → colocaram → £ 2bn e £ 1,4bn , respectivamente</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os investidores → colocaram → en os quais</t>
+          </r>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ Ele → foi seguido → pelos fundos Aviva Investors Multi Strategy Target Return and Income, nos quais os investidores colocaram £ 2bn e £ 1,4bn, respectivamente</t>
           </r>
           <r>
@@ -12751,7 +15216,7 @@
           </r>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12775,7 +15240,7 @@
           </r>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12921,6 +15386,78 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ eles → não se beneficiaram → de a elevação que a queda de a libra deu a os ativos financeiros</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ eles → não se beneficiaram → de a elevação que a queda de a libra deu a os ativos financeiros exteriores</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ eles → não se beneficiaram → de a elevação que a queda de a libra deu exteriores</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a queda de a libra → deu → a os ativos financeiros</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a queda de a libra → deu → a os ativos financeiros exteriores</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ a queda de a libra → deu → a os ativos financeiros que</t>
+          </r>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ Isto → significa → que eles não se beneficiaram da elevação que a queda da libra deu aos ativos financeiros exteriores</t>
           </r>
           <r>
@@ -12961,7 +15498,7 @@
           </r>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12997,7 +15534,7 @@
           </r>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13121,6 +15658,102 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ A Adidas → está ajudando → a limpar os oceanos de a Terra</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A Adidas → está ajudando → a limpar os oceanos de a Terra , usando os resíduos que flutuam por o mundo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A Adidas → está ajudando → a limpar os oceanos de a Terra , usando os resíduos que flutuam por o mundo para fazer sapatos</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A Adidas → está ajudando → usando os resíduos que flutuam por o mundo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A Adidas → está ajudando → usando os resíduos que flutuam para fazer sapatos</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ que → flutuam → por o mundo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ que → flutuam → por o mundo para fazer sapatos</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ que → flutuam → para fazer sapatos</t>
+          </r>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ A Adidas → está ajudando a limpar → os oceanos da Terra, usando os resíduos que flutuam pelo mundo para fazer sapatos</t>
           </r>
           <r>
@@ -13185,7 +15818,7 @@
           </r>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13209,7 +15842,7 @@
           </r>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13306,6 +15939,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ O consumidor → pode impulsionar → a procura por a mudança</t>
+          </r>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
@@ -13313,7 +15959,7 @@
           </r>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13325,7 +15971,7 @@
           </r>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13496,6 +16142,104 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ um relatório importante → disse → Em janeiro</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os oceanos → tomasse → uma atitude radical</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os oceanos → tomasse → uma atitude radical para impedir</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os lixos → vazassem → para os mares</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ os oceanos → conteriam → mais plástico de o que peixes</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ os oceanos → conteriam → mais plástico de o que peixes até 2050</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os oceanos → conteriam → mais plástico de o que peixes até 2050 , a menos que o mundo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os oceanos → conteriam → mais plástico de o que peixes , a menos que o mundo</t>
+          </r>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ um relatório importante → disse → que os oceanos conteriam mais plástico do que peixes até 2050, a menos que o mundo tomasse uma atitude radical para impedir que os lixos vazassem para os mares Em janeiro</t>
           </r>
           <r>
@@ -13560,7 +16304,7 @@
           </r>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13596,7 +16340,7 @@
           </r>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13731,8 +16475,34 @@
               <color rgb="001E7A34"/>
               <sz val="10"/>
             </rPr>
+            <t>✓✓ eu → tive → uma recuperação completa</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓✓ eu → tive → uma recuperação completa Após algumas cirurgias geniais e muito trabalho duro de reabilitação</t>
           </r>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ eu → tive → uma recuperação completa Após algumas cirurgias geniais e muito trabalho duro de reabilitação</t>
+          </r>
           <r>
             <t>
 </t>
@@ -13772,7 +16542,7 @@
           </r>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13785,7 +16555,7 @@
           </r>
         </is>
       </c>
-      <c r="G80" s="3" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13906,6 +16676,90 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓ o SNS → estava → agora sob "" enorme pressão ""</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ o SNS → estava → sob "" enorme pressão ""</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ ele → pediu → a o público</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ ele → pediu → a o público para assumir mais responsabilidade</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ ele → pediu → a o público para assumir mais responsabilidade por a sua própria saúde</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ ele → pediu → a o público Advertindo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ ele → pediu → a o público por a sua própria saúde</t>
+          </r>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -13949,7 +16803,7 @@
           </r>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13985,7 +16839,7 @@
           </r>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14117,6 +16971,92 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ Quatro em cada 10 adultos → ficaram → feridos</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ Quatro em cada 10 adultos → ficaram → feridos devido a o mau tempo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Quatro em cada 10 adultos → ficaram → feridos devido a o mau tempo subestimam , enquanto nove em cada dez</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Quatro em cada 10 adultos → ficaram → feridos devido a o mau tempo subestimam , enquanto nove em cada dez o</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Quatro em cada 10 adultos → ficaram → feridos subestimam , enquanto nove em cada dez</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Quatro em cada 10 adultos → ficaram → feridos o</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ quão fria a Grã - Bretanha → pode ser → en o inverno</t>
+          </r>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
@@ -14161,7 +17101,7 @@
           </r>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr">
+      <c r="G82" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14197,7 +17137,7 @@
           </r>
         </is>
       </c>
-      <c r="G82" s="3" t="inlineStr">
+      <c r="H82" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14308,6 +17248,18 @@
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
+            <t>✓ Eles → vão atuar → en o sábado , 10 de junho</t>
+          </r>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓ Eles → vão atuar → no sábado, 10 de junho</t>
           </r>
           <r>
@@ -14324,7 +17276,7 @@
           </r>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14336,7 +17288,7 @@
           </r>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="H83" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14426,6 +17378,19 @@
             </rPr>
             <t>✓✓ O ano passado → foi → um ano incrível</t>
           </r>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ O ano passado → foi → um ano incrível</t>
+          </r>
           <r>
             <t>
 </t>
@@ -14464,7 +17429,7 @@
           </r>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14501,7 +17466,7 @@
           </r>
         </is>
       </c>
-      <c r="G84" s="3" t="inlineStr">
+      <c r="H84" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14640,6 +17605,90 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Ela → começou → en o RSC</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Ela → começou → en o RSC en o meio de os anos sessenta</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Ela → começou → en o RSC en o meio de os anos sessenta , atuando como internada de asilo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Ela → começou → en o RSC en o meio de os anos sessenta , atuando como internada de asilo en o Marat Sade</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Ela → começou → en o meio de os anos sessenta</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Ela → começou → atuando como internada de asilo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Ela → começou → atuando en o Marat Sade</t>
+          </r>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ Ela → começou → no RSC no meio dos anos sessenta, atuando como internada de asilo no Marat/Sade</t>
           </r>
           <r>
@@ -14680,7 +17729,7 @@
           </r>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14704,7 +17753,7 @@
           </r>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="H85" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14811,6 +17860,19 @@
           </r>
         </is>
       </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ O vestido → é → contemporâneo</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -14870,6 +17932,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -14901,7 +17976,7 @@
           </r>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14925,7 +18000,7 @@
           </r>
         </is>
       </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="H87" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15025,6 +18100,18 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ O seu pescoço → avança → em confronto</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ O seu pescoço → avança → em confronto com veias acentuadas</t>
           </r>
           <r>
@@ -15037,11 +18124,59 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ O seu pescoço → avança → em confronto com veias acentuadas , as suas mãos tremem</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O seu pescoço → avança → com veias acentuadas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O seu pescoço → avança → as suas mãos tremem</t>
+          </r>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O seu pescoço → avança → em confronto com veias acentuadas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t xml:space="preserve">✗ as suas mãos → tremem → </t>
           </r>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="G88" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15065,7 +18200,7 @@
           </r>
         </is>
       </c>
-      <c r="G88" s="3" t="inlineStr">
+      <c r="H88" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15164,6 +18299,31 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="00B8860B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>🟡 Glenda → mandasse → tão bem</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ quem → poderia culpá - → lo</t>
+          </r>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -15196,7 +18356,7 @@
           </r>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15221,7 +18381,7 @@
           </r>
         </is>
       </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="H89" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15370,6 +18530,42 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Ele → trabalhou → en o setor de as notícias</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Ele → trabalhou → en o setor de as notícias e de os assuntos atuais , en a rádio e en a televisão durante décadas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Ele → trabalhou → en o setor e de os assuntos atuais , en a rádio e en a televisão durante décadas</t>
+          </r>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ Ele → trabalhou → no setor das notícias e dos assuntos atuais, na rádio e na televisão durante décadas</t>
           </r>
           <r>
@@ -15422,7 +18618,7 @@
           </r>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15494,7 +18690,7 @@
           </r>
         </is>
       </c>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15604,6 +18800,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -15635,7 +18844,7 @@
           </r>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="G91" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15659,7 +18868,7 @@
           </r>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="H91" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15746,6 +18955,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -15753,7 +18975,7 @@
           </r>
         </is>
       </c>
-      <c r="G92" s="3" t="inlineStr">
+      <c r="H92" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15777,11 +18999,9 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="00C0392B"/>
-              <sz val="10"/>
-            </rPr>
-            <t>⚠ ele → fez → oito longas - metragens</t>
+              <sz val="10"/>
+            </rPr>
+            <t>ele → fez → oito longas - metragens</t>
           </r>
           <r>
             <t>
@@ -15838,6 +19058,43 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ ele → fez → oito longas - metragens</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ ele → fez → Segundo a própria contagem de o diretor</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ ele → fez → Segundo a própria contagem de o diretor , até a a data</t>
+          </r>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -15858,7 +19115,7 @@
           </r>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15883,7 +19140,7 @@
           </r>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="H93" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15984,6 +19241,18 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ Hollywood → tinha → alienado o público familiar</t>
+          </r>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ O cinema → tinha mudado → tão drasticamente que Hollywood tinha alienado o público familiar</t>
           </r>
           <r>
@@ -16014,7 +19283,7 @@
           </r>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="G94" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16052,7 +19321,7 @@
           </r>
         </is>
       </c>
-      <c r="G94" s="3" t="inlineStr">
+      <c r="H94" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16165,6 +19434,90 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ o filme → é um ato → precário , balançando - entre comédias familiares e dramas sociais</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ o filme → é um ato → precário , balançando - entre comédias familiares e dramas sociais profundos</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ o filme → é um ato → de o ponto de vista</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ o filme → é um ato → de o ponto de vista de o realizador</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ o filme → é um ato → balançando - entre comédias familiares e dramas sociais</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ o filme → é um ato → balançando - entre comédias familiares profundos</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ o filme → é → um ato de o ponto de vista</t>
+          </r>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ o filme → é → um ato precário, balançando-se entre comédias familiares e dramas sociais profundos Do ponto de vista do realizador</t>
           </r>
           <r>
@@ -16205,7 +19558,7 @@
           </r>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16253,7 +19606,7 @@
           </r>
         </is>
       </c>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="H95" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16354,6 +19707,66 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ que → parece feito → a a medida</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ que → parece feito → a a medida para uma sessão de domingo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ que → parece feito → a a medida para uma sessão de domingo a a tarde</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ que → parece feito → para uma sessão de domingo</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ que → parece feito → para uma sessão a a tarde</t>
+          </r>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ um aconchegador de corações amigável e despretensioso → parece feito à medida → para uma sessão de domingo à tarde</t>
           </r>
           <r>
@@ -16382,7 +19795,7 @@
           </r>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16406,7 +19819,7 @@
           </r>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr">
+      <c r="H96" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16492,6 +19905,19 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <i val="1"/>
+              <color rgb="00888888"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(nenhuma extração)</t>
+          </r>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -16511,7 +19937,7 @@
           </r>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16547,7 +19973,7 @@
           </r>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="H97" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16606,9 +20032,33 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ O resultado → então , dificilmente é o pijama → de o gato</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
+            <t>✓ O resultado → então , dificilmente é → o pijama de o gato</t>
+          </r>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓ O resultado → então, dificilmente é → o pijama do gato</t>
           </r>
           <r>
@@ -16637,7 +20087,7 @@
           </r>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="G98" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16649,7 +20099,7 @@
           </r>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="H98" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16737,6 +20187,66 @@
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
+            <t>✗ os feitos de Doss → pertencem → a a esfera de o inimaginável</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os feitos de Doss → pertencem → Para as audiências modernas</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os feitos de Doss → pertencem → Para as audiências modernas , maioria</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os feitos de Doss → pertencem → Para as audiências modernas , maioria de as quais</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ os feitos de Doss → pertencem → Para as audiências modernas , maioria de as quais com pouca experiência em conflitos de primeira linha</t>
+          </r>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
             <t>✗ os feitos de Doss → pertencem → à esfera do inimaginável Para as audiências modernas, maioria das quais com pouca experiência em conflitos de primeira linha</t>
           </r>
           <r>
@@ -16753,7 +20263,7 @@
           </r>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16777,7 +20287,7 @@
           </r>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="H99" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16883,6 +20393,43 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001E7A34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✓✓ A história de o Doss → também tem → uma qualidade improvável</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ A história de o Doss → também tem → uma qualidade improvável que torna tudo ainda mais atraente</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ que → torna → tudo ainda mais atraente</t>
+          </r>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="00C0392B"/>
               <sz val="10"/>
             </rPr>
@@ -16915,7 +20462,7 @@
           </r>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16941,7 +20488,7 @@
           </r>
         </is>
       </c>
-      <c r="G100" s="3" t="inlineStr">
+      <c r="H100" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17025,9 +20572,33 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="00C0392B"/>
+              <sz val="10"/>
+            </rPr>
+            <t>✗ Todos os médicos → estavam → armados</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
               <color rgb="004CAF50"/>
               <sz val="10"/>
             </rPr>
+            <t>✓ Todos os médicos → estavam → armados , exceto eu</t>
+          </r>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="004CAF50"/>
+              <sz val="10"/>
+            </rPr>
             <t>✓ Todos os médicos → estavam → armados, exceto eu</t>
           </r>
           <r>
@@ -17044,7 +20615,7 @@
           </r>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17056,7 +20627,7 @@
           </r>
         </is>
       </c>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="H101" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17070,7 +20641,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G101"/>
+  <autoFilter ref="A1:H101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
